--- a/BIDVAutoVS2022/script_data.xlsx
+++ b/BIDVAutoVS2022/script_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cauva\Project\KinhDoanhThe\src\BIDVService\BIDVAutoVS2022\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cauva\Project\KinhDoanhThe\src\BIDVService\BIDVAutoVS2022\bin\Debug\net8.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="dmbgd" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>stt</t>
   </si>
@@ -32,23 +33,107 @@
     <t>on_off</t>
   </si>
   <si>
-    <t>value1</t>
-  </si>
-  <si>
-    <t>value2</t>
-  </si>
-  <si>
-    <t>value3</t>
-  </si>
-  <si>
-    <t>value4</t>
+    <t>phong</t>
+  </si>
+  <si>
+    <t>so_tien</t>
+  </si>
+  <si>
+    <t>ten_cb</t>
+  </si>
+  <si>
+    <t>PHAM THI THU QUYNH - TCHC</t>
+  </si>
+  <si>
+    <t>pgd_duyet</t>
+  </si>
+  <si>
+    <t>nhan</t>
+  </si>
+  <si>
+    <t>han_muc</t>
+  </si>
+  <si>
+    <t>so_hieu_vb</t>
+  </si>
+  <si>
+    <t>ngay_hl</t>
+  </si>
+  <si>
+    <t>mat_hang</t>
+  </si>
+  <si>
+    <t>is_qua_tang</t>
+  </si>
+  <si>
+    <t>NUOC UONG</t>
+  </si>
+  <si>
+    <t>nd_trich_yeu</t>
+  </si>
+  <si>
+    <t>TIEP KHACH HANG CONG TY TNHH THUONG MAI FRESH AND GREEN - CIF23357966</t>
+  </si>
+  <si>
+    <t>ten</t>
+  </si>
+  <si>
+    <t>ten_ngan</t>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>gia tri day du</t>
+  </si>
+  <si>
+    <t>viet</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Việt</t>
+  </si>
+  <si>
+    <t>tra</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trà</t>
+  </si>
+  <si>
+    <t>hong</t>
+  </si>
+  <si>
+    <t>linh</t>
+  </si>
+  <si>
+    <t>quang</t>
+  </si>
+  <si>
+    <t>Lê Thị Kim Nhạn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Hồng</t>
+  </si>
+  <si>
+    <t>Trần Thành Linh</t>
+  </si>
+  <si>
+    <t>Đỗ Anh Quang</t>
+  </si>
+  <si>
+    <t>name_pgd</t>
+  </si>
+  <si>
+    <t>san_pham</t>
+  </si>
+  <si>
+    <t>pk_kh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,13 +141,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -77,8 +176,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -359,27 +471,358 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="17.21875" customWidth="1"/>
+    <col min="5" max="6" width="17.21875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="33.6640625" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="21.88671875" style="7" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>521</v>
+      </c>
+      <c r="D2" s="1">
+        <v>3910000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>22952</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46059</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="O2" s="7">
+        <f>VLOOKUP(H2,dmbgd!A:D,2,0)</f>
+        <v>133598</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O3" s="7" t="e">
+        <f>VLOOKUP(H3,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O4" s="7" t="e">
+        <f>VLOOKUP(H4,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O5" s="7" t="e">
+        <f>VLOOKUP(H5,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O6" s="7" t="e">
+        <f>VLOOKUP(H6,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O7" s="7" t="e">
+        <f>VLOOKUP(H7,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O8" s="7" t="e">
+        <f>VLOOKUP(H8,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O9" s="7" t="e">
+        <f>VLOOKUP(H9,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O10" s="7" t="e">
+        <f>VLOOKUP(H10,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O11" s="7" t="e">
+        <f>VLOOKUP(H11,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O12" s="7" t="e">
+        <f>VLOOKUP(H12,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O13" s="7" t="e">
+        <f>VLOOKUP(H13,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O14" s="7" t="e">
+        <f>VLOOKUP(H14,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O15" s="7" t="e">
+        <f>VLOOKUP(H15,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O16" s="7" t="e">
+        <f>VLOOKUP(H16,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O17" s="7" t="e">
+        <f>VLOOKUP(H17,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O18" s="7" t="e">
+        <f>VLOOKUP(H18,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O19" s="7" t="e">
+        <f>VLOOKUP(H19,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O20" s="7" t="e">
+        <f>VLOOKUP(H20,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O21" s="7" t="e">
+        <f>VLOOKUP(H21,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O22" s="7" t="e">
+        <f>VLOOKUP(H22,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O23" s="7" t="e">
+        <f>VLOOKUP(H23,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O24" s="7" t="e">
+        <f>VLOOKUP(H24,dmbgd!A:D,2,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>133361</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="str">
+        <f>B2 &amp; " - " &amp; C2</f>
+        <v>133361 - Lê Hoàng Việt</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>149200</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D7" si="0">B3 &amp; " - " &amp; C3</f>
+        <v>149200 - Lê Thanh Trà</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>133598</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>133598 - Lê Thị Kim Nhạn</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>133471</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>133471 - Nguyễn Thị Kim Hồng</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>155674</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>155674 - Trần Thành Linh</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>153933</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>153933 - Đỗ Anh Quang</v>
       </c>
     </row>
   </sheetData>
